--- a/feedback_surveys/025_diversity_program_awareness_survey--feedback_surveys.xlsx
+++ b/feedback_surveys/025_diversity_program_awareness_survey--feedback_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -749,7 +749,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>through_workshops_and_trainings</t>
+          <t>through workshops and trainings</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>through_diversity_committee</t>
+          <t>through diversity committee</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>through_leadership</t>
+          <t>through leadership</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>through_newsletters</t>
+          <t>through newsletters</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>through_other</t>
+          <t>through other</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>very_positive</t>
+          <t>very positive</t>
         </is>
       </c>
     </row>
@@ -885,7 +885,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>somewhat_positive</t>
+          <t>somewhat positive</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>somewhat_negative</t>
+          <t>somewhat negative</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>very_negative</t>
+          <t>very negative</t>
         </is>
       </c>
     </row>
